--- a/plantillas/41.xlsx
+++ b/plantillas/41.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cargue" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listas" sheetId="2" state="hidden" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Productos" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet name="Cargue" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Listas" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet name="Productos" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="MARCA_1">Listas!$D$2:$D$4</definedName>
@@ -9192,7 +9192,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -9272,7 +9272,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -9432,7 +9432,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -9472,7 +9472,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -9752,7 +9752,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -10572,7 +10572,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -10910,7 +10910,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>24.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
     </row>

--- a/plantillas/41.xlsx
+++ b/plantillas/41.xlsx
@@ -9332,7 +9332,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -9432,7 +9432,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -9912,7 +9912,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -10910,7 +10910,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>28.10.2026</t>
+          <t>29.10.2026</t>
         </is>
       </c>
     </row>

--- a/plantillas/41.xlsx
+++ b/plantillas/41.xlsx
@@ -9332,7 +9332,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -10910,7 +10910,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>30.10.2026</t>
         </is>
       </c>
     </row>
